--- a/docs_scan/TEM NHẬN DIỆN HÀNG HÓA THÀNH A4.xlsx
+++ b/docs_scan/TEM NHẬN DIỆN HÀNG HÓA THÀNH A4.xlsx
@@ -1,48 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KhoHCM\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345E6C80-4A60-4556-A763-9CD35D6D3D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="135" windowWidth="14760" windowHeight="15345" xr2:uid="{37E99E8C-831C-4D11-8000-1DC4AF2278A8}"/>
+    <workbookView windowWidth="28245" windowHeight="14130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t xml:space="preserve">              TEM NHẬN DIỆN HÀNG HÓA</t>
   </si>
   <si>
-    <t>KHO : SPIDER</t>
+    <t>KHO : xxxx</t>
   </si>
   <si>
-    <t>NGƯỜI ĐIỀU HÀNH :</t>
+    <t>TÊN HÀNG:</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÃ ĐƠN HÀNG :        </t>
   </si>
   <si>
     <t xml:space="preserve">NGÀY NHẬP : </t>
   </si>
   <si>
-    <t xml:space="preserve"> CHỨNG TỪ : </t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">SỐ LƯỢNG :                                        </t>
     </r>
     <r>
@@ -51,11 +51,14 @@
         <sz val="24"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  10</t>
     </r>
+  </si>
+  <si>
+    <t>/80</t>
   </si>
   <si>
     <t xml:space="preserve">PALET SỐ : </t>
@@ -65,6 +68,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">NGƯỜI NHẬP :                            </t>
     </r>
     <r>
@@ -73,7 +84,7 @@
         <sz val="24"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>LINH</t>
@@ -81,6 +92,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">GIAO ĐẾN :                                 </t>
     </r>
     <r>
@@ -89,29 +108,37 @@
         <sz val="24"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">              Bình Định</t>
     </r>
   </si>
-  <si>
-    <t xml:space="preserve">MÃ ĐƠN HÀNG :        </t>
-  </si>
-  <si>
-    <t>TÊN HÀNG:</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -119,15 +146,7 @@
       <sz val="36"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,7 +154,47 @@
       <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="50"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="40"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="25"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -143,23 +202,158 @@
       <sz val="22"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="50"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -167,43 +361,205 @@
       <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="40"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="25"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -213,86 +569,372 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Check Cell" xfId="7" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="8" builtinId="17"/>
+    <cellStyle name="Note" xfId="9" builtinId="10"/>
+    <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
+    <cellStyle name="60% - Accent4" xfId="11" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="Title" xfId="16" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
+    <cellStyle name="Input" xfId="21" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
+    <cellStyle name="Good" xfId="23" builtinId="26"/>
+    <cellStyle name="Output" xfId="24" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bad" xfId="29" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -308,19 +950,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{167200E6-BB96-453F-8F32-72D76DCA8B4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -333,8 +969,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="119062" y="0"/>
-          <a:ext cx="1654969" cy="803879"/>
+          <a:off x="118745" y="0"/>
+          <a:ext cx="1654810" cy="798830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -389,7 +1025,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -422,26 +1058,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -474,23 +1093,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -632,67 +1234,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9637E41F-F797-4D57-86E4-0F234C5DFDF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:L10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="0.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="12" max="12" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="6.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="18.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="0.714285714285714" customWidth="1"/>
+    <col min="8" max="8" width="13.8571428571429" customWidth="1"/>
+    <col min="12" max="12" width="21.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="2" ht="46.5" spans="1:12">
       <c r="A2" s="1"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="50.25" customHeight="1" spans="1:12">
       <c r="A3" s="1"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="2"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -706,110 +1302,118 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="79.5" customHeight="1" spans="1:12">
       <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+    </row>
+    <row r="6" ht="53.25" customHeight="1" spans="1:12">
+      <c r="A6" s="1"/>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" ht="51" spans="1:12">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" ht="33.75" spans="1:12">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" ht="45" customHeight="1" spans="1:12">
+      <c r="A9" s="1"/>
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
+    <row r="10" ht="132" customHeight="1" spans="1:12">
+      <c r="A10" s="1"/>
+      <c r="B10" s="6" t="s">
+        <v>11</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="C5:L5"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:L6"/>
@@ -817,15 +1421,12 @@
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="J8:L8"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C10:L10"/>
   </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.708661417322835" right="0.708661417322835" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="95" orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>